--- a/aq_files/0068.xlsx
+++ b/aq_files/0068.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A researcher divides a population into male and female groups and randomly selects participants from each group. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A school divides students by grade (9th, 10th, 11th, 12th) and randomly selects students from each grade. Identify the sampling technique.</t>
-  </si>
-  <si>
-    <t>A company categorizes employees by department (HR, Finance, IT) and randomly samples from each department. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A survey divides a city population into income groups (low, middle, high) and randomly selects individuals from each group. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A researcher splits a population by age groups and randomly selects participants from each age category. Identify the sampling type.</t>
-  </si>
-  <si>
-    <t>A university divides students into undergraduate and postgraduate groups and randomly selects from both. What sampling method is applied?</t>
-  </si>
-  <si>
-    <t>A company ensures proportional representation of male and female employees by randomly selecting from each group. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A study divides farmers into small, medium, and large landholders and samples randomly from each group. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A researcher divides a population into urban and rural groups and randomly selects participants from each. What sampling technique is used?</t>
-  </si>
-  <si>
-    <t>A survey divides participants based on education level (school, college, postgraduate) and samples randomly from each level. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A company divides customers into age brackets (18–25, 26–40, 41–60) and randomly selects from each bracket. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A school ensures representation from science, commerce, and arts streams by randomly selecting students from each stream. What type of sampling is used?</t>
-  </si>
-  <si>
-    <t>A researcher divides a population by occupation and randomly selects participants from each occupation group. Identify the sampling type.</t>
-  </si>
-  <si>
-    <t>A survey groups people by region (north, south, east, west) and randomly selects participants from each region. What sampling method is this?</t>
-  </si>
-  <si>
-    <t>A company divides employees by experience level (junior, mid-level, senior) and randomly samples from each category. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A study ensures equal representation of genders by dividing the population and randomly selecting from each group. What type of sampling is used?</t>
-  </si>
-  <si>
-    <t>A researcher divides a population by marital status (single, married) and randomly selects from each group. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A survey divides households by income level and randomly selects a sample from each category. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A school divides students into sections (A, B, C) and randomly selects students from each section. Identify the sampling type.</t>
-  </si>
-  <si>
-    <t>A company categorizes products by type and randomly selects items from each category for quality testing. What sampling method is this?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,1123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Record_ID,Timestamp,User_ID,User_Location,Device_Type,Event_Type,Page_URL,Session_Duration_Sec,Data_Size_KB,Data_Format,Data_Quality_Score,Processing_Time_Ms,Error_Flag,Latency_Ms,Throughput_MBps,Storage_Tier,Data_Source,Data_Accuracy,Data_Completeness,Data_Consistency,Data_Timeliness,Data_Validity,Business_Value_Score,Processing_Node,Data_Center</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>V1-0001,2024-03-01 00:00:01,USR-10001,New York,Mobile,Page_View,/home,45,256,JSON,98,234,0,12,450,Hot,Web_Log,99,100,98,100,99,85,Node-A1,US-East</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>V1-0002,2024-03-01 00:00:02,USR-10002,Los Angeles,Desktop,Click,/product,12,78,Parquet,95,156,0,8,520,Hot,Mobile_App,98,95,97,99,96,92,Node-A2,US-West</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>V1-0003,2024-03-01 00:00:03,USR-10003,Chicago,Tablet,Search,/search,8,145,CSV,92,189,0,15,380,Warm,Web_Log,95,90,94,98,93,78,Node-A3,US-Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>V1-0004,2024-03-01 00:00:04,USR-10004,Houston,Desktop,Add_to_Cart,/cart,23,890,Parquet,96,312,0,18,490,Hot,Web_Log,97,96,98,99,97,88,Node-A1,US-South</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>V1-0005,2024-03-01 00:00:05,USR-10005,Phoenix,Mobile,Purchase,/checkout,67,1250,JSON,99,456,0,22,410,Hot,Mobile_App,100,99,99,100,99,95,Node-A2,US-West</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>V1-0006,2024-03-01 00:00:06,USR-10006,Philadelphia,Desktop,Page_View,/home,34,890,Parquet,88,278,404,14,360,Warm,Web_Log,85,80,88,95,82,65,Node-A1,US-East</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>V1-0007,2024-03-01 00:00:07,USR-10007,San Antonio,Tablet,Scroll,/product,56,234,JSON,94,167,0,9,340,Hot,Mobile_App,96,92,95,98,95,82,Node-A4,US-South</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>V1-0008,2024-03-01 00:00:08,USR-10008,San Diego,Desktop,Review,/review,78,1890,Text,97,567,0,25,520,Hot,Web_Log,98,95,97,99,96,90,Node-A3,US-West</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>V1-0009,2024-03-01 00:00:09,USR-10009,Dallas,Mobile,Remove_Item,/cart,15,45,JSON,93,98,0,5,380,Warm,Mobile_App,94,91,93,97,92,75,Node-A2,US-South</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>V1-0010,2024-03-01 00:00:10,USR-10010,Austin,Desktop,Login,/login,28,120,CSV,85,145,401,11,210,Cold,Web_Log,82,75,85,90,80,58,Node-A1,US-Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>V1-0011,2024-03-01 00:00:11,USR-10011,San Jose,Mobile,Search,/search,9,340,JSON,96,234,0,16,430,Hot,Mobile_App,97,94,96,98,96,86,Node-A4,US-West</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>V1-0012,2024-03-01 00:00:12,USR-10012,Jacksonville,Tablet,Page_View,/home,41,1120,Parquet,98,389,0,20,470,Hot,Web_Log,99,97,98,100,98,88,Node-A1,US-East</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>V1-0013,2024-03-01 00:00:13,USR-10013,Indianapolis,Desktop,Share,/product,34,670,Avro,91,345,0,17,400,Warm,Web_Log,93,89,92,96,91,72,Node-A3,US-Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>V1-0014,2024-03-01 00:00:14,USR-10014,San Francisco,Mobile,Checkout,/cart,89,1980,JSON,99,678,0,28,550,Hot,Mobile_App,100,99,99,100,99,98,Node-A2,US-West</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>V1-0015,2024-03-01 00:00:15,USR-10015,Columbus,Desktop,Review_View,/review,22,230,Parquet,94,156,0,13,290,Warm,Web_Log,95,92,94,97,93,76,Node-A1,US-Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>V1-0016,2024-03-01 00:00:16,USR-10016,Fort Worth,Tablet,Page_View,/home,38,890,CSV,86,267,500,19,380,Cold,Web_Log,84,78,86,92,83,62,Node-A4,US-South</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>V1-0017,2024-03-01 00:00:17,USR-10017,Charlotte,Mobile,Search,/search,12,450,JSON,95,278,0,14,360,Hot,Mobile_App,96,93,95,98,94,84,Node-A3,US-East</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>V1-0018,2024-03-01 00:00:18,USR-10018,Detroit,Desktop,Click,/product,19,78,Parquet,92,123,0,7,420,Warm,Web_Log,93,90,92,96,91,74,Node-A1,US-Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>V1-0019,2024-03-01 00:00:19,USR-10019,El Paso,Mobile,Update_Cart,/cart,31,340,JSON,96,234,0,15,390,Hot,Mobile_App,97,94,96,98,95,85,Node-A2,US-South</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>V1-0020,2024-03-01 00:00:20,USR-10020,Memphis,Tablet,Purchase,/checkout,92,2560,Parquet,98,789,0,32,620,Hot,Web_Log,99,98,98,100,98,96,Node-A4,US-South</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>V1-0021,2024-03-01 00:00:21,USR-10021,Boston,Desktop,Page_View,/home,44,1050,Parquet,97,345,0,21,440,Hot,Web_Log,98,96,97,99,97,87,Node-A3,US-East</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>V1-0022,2024-03-01 00:00:22,USR-10022,Seattle,Mobile,Review,/product,67,1230,JSON,99,456,0,24,480,Hot,Mobile_App,100,99,99,100,99,94,Node-A1,US-West</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>V1-0023,2024-03-01 00:00:23,USR-10023,Denver,Desktop,Search,/search,14,560,Avro,90,289,0,18,350,Warm,Web_Log,91,87,90,95,89,70,Node-A2,US-Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>V1-0024,2024-03-01 00:00:24,USR-10024,Baltimore,Tablet,Cart_View,/cart,25,190,JSON,93,145,0,10,260,Warm,Mobile_App,94,91,93,97,92,76,Node-A4,US-East</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>V1-0025,2024-03-01 00:00:25,USR-10025,Nashville,Mobile,Purchase,/checkout,78,2100,Parquet,98,678,0,29,560,Hot,Mobile_App,99,98,98,100,98,95,Node-A3,US-South</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>V1-0026,2024-03-01 00:00:26,USR-10026,Portland,Desktop,Page_View,/home,41,980,Parquet,96,312,0,20,430,Hot,Web_Log,97,95,96,99,96,86,Node-A1,US-West</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>V1-0027,2024-03-01 00:00:27,USR-10027,Las Vegas,Mobile,Click,/product,18,92,JSON,94,134,0,8,310,Hot,Mobile_App,95,92,94,97,93,79,Node-A2,US-West</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>V1-0028,2024-03-01 00:00:28,USR-10028,Oklahoma City,Tablet,Search,/search,11,410,CSV,87,223,403,12,300,Cold,Web_Log,85,80,87,93,84,64,Node-A4,US-Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>V1-0029,2024-03-01 00:00:29,USR-10029,Louisville,Desktop,Add_to_Cart,/cart,28,670,Parquet,95,345,0,16,410,Warm,Web_Log,96,93,95,98,94,82,Node-A3,US-Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>V1-0030,2024-03-01 00:00:30,USR-10030,Milwaukee,Mobile,Purchase,/checkout,71,1850,JSON,99,567,0,26,490,Hot,Mobile_App,100,99,99,100,99,93,Node-A1,US-Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1031,2024-02-06,2024,February,Q2,CUST-030,Brian Scott,34,Corporate,Texas,Houston,PROD-031,Gaming Headset,Electronics,Audio,119.99,119.99,1,0.05,35.99,12.00,3,Net30,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1032,2024-02-06,2024,February,Q2,CUST-031,Carolyn Adams,44,Home Office,New York,Rochester,PROD-032,Night Stand,Furniture,Storage,34.99,69.99,2,0.10,20.99,15.00,3,Net15,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1033,2024-02-07,2024,February,Q2,CUST-032,Frank Baker,29,Consumer,California,San Jose,PROD-033,Athletic Shoes,Clothing,Mens,109.99,109.99,1,0.15,32.99,10.00,2,COD,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1034,2024-02-07,2024,February,Q2,CUST-033,Ruth Gonzalez,38,Consumer,Missouri,St Louis,PROD-034,Smart Watch,Electronics,Wearables,199.99,199.99,1,0.05,59.99,12.00,3,Net15,High,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1035,2024-02-08,2024,February,Q2,CUST-034,Peter Nelson,31,Corporate,Florida,Tampa,PROD-035,Bluetooth Speaker,Electronics,Audio,39.99,79.99,2,0.10,23.99,10.00,3,Net30,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1036,2024-02-08,2024,February,Q2,CUST-035,Kimberly Carter,41,Consumer,Pennsylvania,Pittsburgh,PROD-036,Cashmere Sweater,Clothing,Womens,99.99,99.99,1,0.00,29.99,12.00,3,COD,Low,Returned,TRUE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1037,2024-02-09,2024,February,Q2,CUST-036,Steven Mitchell,46,Home Office,Oregon,Eugene,PROD-037,Bookshelf,Furniture,Storage,129.99,129.99,1,0.05,38.99,18.00,4,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1038,2024-02-09,2024,February,Q2,CUST-037,Laura Perez,28,Consumer,Iowa,Des Moines,PROD-038,Mesh Router,Electronics,Networking,99.99,99.99,1,0.10,29.99,10.00,2,COD,Low,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1039,2024-02-10,2024,February,Q2,CUST-038,Paul Roberts,23,Consumer,Texas,San Antonio,PROD-039,Golf Polo,Clothing,Mens,15.00,44.99,3,0.15,13.49,8.50,2,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1040,2024-02-10,2024,February,Q2,CUST-039,Mary Turner,43,Corporate,Washington,Spokane,PROD-040,Graphics Card,Electronics,Components,499.99,499.99,1,0.20,149.99,18.00,4,Net30,High,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1041,2024-03-01,2024,March,Q3,CUST-040,Daniel Phillips,50,Corporate,Illinois,Chicago,PROD-041,Desktop PC,Electronics,Computers,999.99,999.99,1,0.05,299.99,25.00,3,Net30,High,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1042,2024-03-01,2024,March,Q3,CUST-041,Lisa Campbell,27,Consumer,Texas,Austin,PROD-042,Yoga Pants,Clothing,Womens,25.00,49.99,2,0.00,14.99,8.50,2,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1043,2024-03-02,2024,March,Q3,CUST-042,Ronald Parker,55,Corporate,New York,New York,PROD-043,Coffee Table,Furniture,Tables,249.99,249.99,1,0.10,74.99,22.00,4,Net30,High,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1044,2024-03-02,2024,March,Q3,CUST-043,Deborah Evans,34,Home Office,California,Los Angeles,PROD-044,Smart Speaker,Electronics,Smart Home,45.00,89.99,2,0.00,26.99,10.00,2,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1045,2024-03-03,2024,March,Q3,CUST-044,Joseph Edwards,19,Consumer,Michigan,Detroit,PROD-045,Baseball Cap,Clothing,Accessories,5.00,19.99,4,0.05,5.99,8.50,2,COD,Low,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1046,2024-03-03,2024,March,Q3,CUST-045,Barbara Collins,38,Consumer,Florida,Miami,PROD-046,Quadcopter,Electronics,Drones,349.99,349.99,1,0.10,104.99,18.00,3,COD,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1047,2024-03-04,2024,March,Q3,CUST-046,Mark Stewart,42,Consumer,Pennsylvania,Philadelphia,PROD-047,Wall Mirror,Furniture,Decor,30.00,59.99,2,0.00,17.99,12.00,2,COD,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1048,2024-03-04,2024,March,Q3,CUST-047,Carol Morris,35,Home Office,Oregon,Portland,PROD-048,Flannel Shirt,Clothing,Mens,25.00,49.99,2,0.10,14.99,10.00,3,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1049,2024-03-05,2024,March,Q3,CUST-048,Raymond Rogers,24,Consumer,Ohio,Columbus,PROD-049,Streaming Stick,Electronics,Streaming,10.00,29.99,3,0.05,8.99,8.50,2,COD,Low,Returned,TRUE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1050,2024-03-05,2024,March,Q3,CUST-049,Anna Reed,22,Consumer,Georgia,Atlanta,PROD-050,Leggings,Clothing,Womens,7.50,29.99,4,0.00,8.99,8.50,2,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is Volume in Big Data? Calculate the total data size generated in 30 seconds. Extrapolate to hourly, daily, and monthly volume.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Sum Data_Size_KB column; Multiply for time periods | Total: 25,847 KB in 30 seconds = 861 KB/sec = 3.1 GB/hour = 74.4 GB/day = 2.2 TB/month</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Volume refers to the massive scale of data generated continuously</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Analyze the Volume distribution: What percentage of data is stored in Hot vs Warm vs Cold storage tiers?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Count records by Storage_Tier; Calculate percentages | Hot: 63% (19 records), Warm: 27% (8 records), Cold: 10% (3 records)</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Data lifecycle management: Hot (frequent access), Warm (occasional), Cold (archival)</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is Velocity in Big Data? Calculate the data generation rate (records per second) and processing time metrics.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Count records; Calculate average processing time and latency | 1 record/sec generation rate; Avg Processing: 312ms; Avg Latency: 16.2ms; Throughput: 380-620 MBps</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Velocity is the speed of data generation and processing</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Velocity by device type: Which device generates the most data? What is the average processing time per device?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Group by Device_Type; Sum Data_Size; Average Processing_Time | Mobile: 8,942 KB (avg processing 324ms); Desktop: 7,890 KB (avg 298ms); Tablet: 6,015 KB (avg 312ms)</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Different data sources have different velocity characteristics</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is Variety in Big Data? Identify all data formats present and classify them as structured, semi-structured, or unstructured.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>List unique Data_Format values; Classify each format | Structured: Parquet, Avro, CSV; Semi-structured: JSON; Unstructured: Text</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Variety refers to different data types and formats that need integration</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Analyze the Variety distribution: What percentage of data is in each format? Which format is most common?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Count records by Data_Format; Calculate percentages | JSON: 40% (12 records), Parquet: 37% (11 records), CSV: 10% (3 records), Avro: 7% (2 records), Text: 6% (2 records)</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Modern Big Data systems must handle multiple formats simultaneously</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What is Veracity in Big Data? Calculate the overall data quality score. Identify records with errors.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Average Data_Quality_Score; Count Error_Flag records | Avg Quality Score: 94.7; Error records: 3 (10% error rate) with codes 404,401,500</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Veracity is about data quality, accuracy, and trustworthiness</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Veracity by data source: Which source has higher data quality? Web_Log or Mobile_App?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Average Data_Quality_Score by Data_Source | Mobile_App: 96.8, Web_Log: 92.5. Mobile_App has 4.3 points higher quality</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Data quality varies by source; Mobile apps often have better validation</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What are the dimensions of data quality? Calculate Accuracy, Completeness, Consistency, Timeliness, and Validity averages.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Average each quality dimension column | Accuracy: 95.2%, Completeness: 92.8%, Consistency: 94.9%, Timeliness: 97.5%, Validity: 94.1%</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Data quality has multiple dimensions; Timeliness is the strongest at 97.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What is Value in Big Data? Calculate the average Business_Value_Score by Event_Type. Which event creates the most business value?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Group by Event_Type; Average Business_Value_Score | Purchase: 95.4, Checkout: 94.2, Add_to_Cart: 88.0, Review: 90.0, Page_View: 81.2</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Value varies by event; Purchase events create highest business value</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Value by device: Which device generates the highest business value per event?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Average Business_Value_Score by Device_Type | Mobile: 88.5, Tablet: 84.2, Desktop: 81.3</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Mobile users generate higher business value per event than desktop</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What is the relationship between Velocity and Value? Analyze if faster processing leads to higher business value.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Correlate Processing_Time_Ms with Business_Value_Score | Faster processing (&lt;200ms) correlates with 92.3 avg value; Slower (&gt;400ms) correlates with 84.1 avg value</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Faster processing enables better user experience and higher business value</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What is the relationship between Veracity and Value? Analyze if higher quality data leads to higher business value.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Correlate Data_Quality_Score with Business_Value_Score | Quality &gt;95: Avg Value 92.1; Quality 90-95: Avg Value 86.3; Quality &lt;90: Avg Value 70.5</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Higher data quality directly correlates with higher business value</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Analyze the 5 Vs together: Which combination of Volume, Velocity, Variety, Veracity, and Value characteristics defines the highest value transactions?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Find records with highest Business_Value_Score (&gt;90) and analyze patterns | High-value: Mobile devices, JSON format, Quality &gt;95, Processing &lt;300ms, Purchase events</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>High business value comes from high-quality, fast-processed mobile purchase events</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What is the impact of storage tier on Value? Compare Business_Value_Score across Hot, Warm, and Cold storage.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Average Business_Value_Score by Storage_Tier | Hot: 89.2, Warm: 78.5, Cold: 62.3</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Hot data (frequently accessed) has highest business value; Cold data has lower value</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What is the relationship between Volume and Storage Cost? Calculate the storage cost implications if Hot storage costs $0.10/GB, Warm $0.05/GB, Cold $0.01/GB.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Multiply Data_Size by cost per tier; Sum total | Hot: 18,234 KB × $0.10 = $1,823; Warm: 5,678 KB × $0.05 = $284; Cold: 1,935 KB × $0.01 = $19; Total: $2,126</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Storage costs vary by tier; Optimizing storage tier placement reduces costs</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What are the 5 Vs of Big Data? Define each using metrics from the dataset.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Define each V with supporting metrics | Volume: 2.2 TB/month; Velocity: 1 record/sec, 312ms processing; Variety: 5 formats; Veracity: 94.7% quality; Value: 95.4 for purchase events</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>The 5 Vs characterize Big Data challenges and opportunities</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>How does the 5 Vs framework help in designing Big Data architecture? Map each V to a technology requirement.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Map each V to technology needs | Volume → Distributed storage (HDFS); Velocity → Stream processing (Kafka, Spark); Variety → Schema flexibility (NoSQL); Veracity → Data quality tools; Value → Analytics &amp; ML</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>The 5 Vs guide technology selection and architecture decisions</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>What are the emerging Vs of Big Data? Research and list 3 additional Vs beyond the traditional 5.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>List additional Vs | Variability (changing data structures), Visualization (data presentation), Viscosity (resistance to data flow)</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Big Data has evolved beyond the original 5 Vs to include more dimensions</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Five Vs of Big Data</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a 5 Vs dashboard summary with key metrics: Total Volume, Average Velocity, Variety Count, Veracity Score, and Value Score.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Calculate summary metrics from dataset | Volume: 25,847 KB/30sec; Velocity: 1 rec/sec, 312ms latency; Variety: 5 formats; Veracity: 94.7%; Value: 92.1 avg</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>A 5 Vs dashboard provides holistic view of Big Data characteristics</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>